--- a/public/Guia/Rec-CuentasConceptos2.xlsx
+++ b/public/Guia/Rec-CuentasConceptos2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SAC-IPE\public\Guia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F3B649-A5C6-4FBE-B4EA-831C3FD93290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1050C76E-CF3C-42BB-8909-08008920A562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
   <si>
     <t>cuenta</t>
   </si>
@@ -50,50 +50,152 @@
     <t>tipo</t>
   </si>
   <si>
-    <t>II.1.2 CUOTAS Y APORTACIONES DE SEGURIDAD SOCIAL</t>
-  </si>
-  <si>
-    <t>a) Por la recaudación en efectivo de cuotas y aportaciones de seguridad social determinables, recibidas en la Tesorería y/o auxiliares de la misma. b) Por la recaudación en efectivo de parcialidades o pago diferido, derivada del convenio formalizado para pago de cuotas y aportaciones de seguridad social. c) Por la recaudación en efectivo de la resolución judicial definitiva por incumplimiento de pago de cuotas y aportaciones de seguridad social. e) Por la recaudación en efectivo por deudores morosos por incumplimiento de pago de cuotas y aportaciones de seguridad social. f) Por la recaudación en efectivo de cuotas y aportaciones de seguridad social autodeterminables, recibidas en la Tesorería y/o auxiliares de la misma.</t>
-  </si>
-  <si>
-    <t>Por el recaudo de ingresos por venta de bienes y prestación de servicios</t>
-  </si>
-  <si>
-    <t>II.1.7.1 VENTA DE BIENES Y PRESTACIÓN DE SERVICIOS (VENTAS)</t>
-  </si>
-  <si>
-    <t>Por el recaudo de ingresos de aportaciones. 1</t>
-  </si>
-  <si>
-    <t>Por el recaudo de ingresos de subsidios y subvenciones.</t>
-  </si>
-  <si>
     <t>II.1.8 PARTICIPACIONES, APORTACIONES, CONVENIOS, INCENTIVOS DERIVADOS DE LA COLABORACIÓN FISCAL, FONDOS DISTINTOS DE APORTACIONES, TRANSFERENCIAS, ASIGNACIONES, SUBSIDIOS Y SUBVENCIONES, Y PENSIONES Y JUBILACIONES</t>
   </si>
   <si>
-    <t>Por el recaudo de otros ingresos propios por pensiones.</t>
-  </si>
-  <si>
-    <t>2.1.9.1.01.01</t>
-  </si>
-  <si>
-    <t>2.1.9.1.01.02</t>
-  </si>
-  <si>
-    <t>2.1.9.1.01.03</t>
-  </si>
-  <si>
-    <t>2.1.9.1.01.04</t>
-  </si>
-  <si>
-    <t>2.1.9.1.01.05</t>
+    <t>Por el recaudo de ingresos de Compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.5.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.13</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.06</t>
+  </si>
+  <si>
+    <t>1.1.1.2.03.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.03.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.07.01</t>
+  </si>
+  <si>
+    <t>Presupuestal - Abono</t>
+  </si>
+  <si>
+    <t>Presupuestal - Cargo</t>
+  </si>
+  <si>
+    <t>Contable - Abono</t>
+  </si>
+  <si>
+    <t>Contable - Cargo</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.08</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.5.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.14</t>
+  </si>
+  <si>
+    <t>1.1.1.1.01.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1.2.02.02 </t>
+  </si>
+  <si>
+    <t>Por la recaudación en efectivo o transferencia de otros ingresos propios derivados de Comisiones por retención en prestaciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,19 +209,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -136,9 +238,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,13 +553,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A46DBC-EF38-4A4C-B82B-A7E0178DC86F}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="125" customWidth="1"/>
     <col min="3" max="3" width="69.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -476,59 +576,564 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/Guia/Rec-CuentasConceptos2.xlsx
+++ b/public/Guia/Rec-CuentasConceptos2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1050C76E-CF3C-42BB-8909-08008920A562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5894258-92BF-4DE6-BDD1-0A4C1E2272EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -53,133 +53,133 @@
     <t>II.1.8 PARTICIPACIONES, APORTACIONES, CONVENIOS, INCENTIVOS DERIVADOS DE LA COLABORACIÓN FISCAL, FONDOS DISTINTOS DE APORTACIONES, TRANSFERENCIAS, ASIGNACIONES, SUBSIDIOS Y SUBVENCIONES, Y PENSIONES Y JUBILACIONES</t>
   </si>
   <si>
+    <t>Presupuestal - Abono</t>
+  </si>
+  <si>
+    <t>Presupuestal - Cargo</t>
+  </si>
+  <si>
+    <t>Contable - Abono</t>
+  </si>
+  <si>
+    <t>Contable - Cargo</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.08</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.5.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el recaudo de ingresos de Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.5.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>1.1.2.9.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.01.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.06</t>
+  </si>
+  <si>
+    <t>1.1.1.2.03.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.03.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.04.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.05.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.01</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.03</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.04</t>
+  </si>
+  <si>
+    <t>1.1.1.2.06.05</t>
+  </si>
+  <si>
+    <t>1.1.1.2.07.01</t>
+  </si>
+  <si>
     <t>Por el recaudo de ingresos de Compensación bancaria de recursos propios</t>
   </si>
   <si>
-    <t>8.1.5.4.3.9.9.01.13</t>
-  </si>
-  <si>
-    <t>8.1.4.4.3.9.9.01.13</t>
+    <t>8.1.5.4.1.7.1.02.02</t>
+  </si>
+  <si>
+    <t>8.1.4.4.1.7.1.02.02</t>
   </si>
   <si>
     <t>1.1.2.2.02.13</t>
-  </si>
-  <si>
-    <t>1.1.1.2.01.01</t>
-  </si>
-  <si>
-    <t>1.1.1.2.01.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.01.03</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.01</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.03</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.04</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.05</t>
-  </si>
-  <si>
-    <t>1.1.1.2.02.06</t>
-  </si>
-  <si>
-    <t>1.1.1.2.03.01</t>
-  </si>
-  <si>
-    <t>1.1.1.2.03.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.04.01</t>
-  </si>
-  <si>
-    <t>1.1.1.2.04.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.04.03</t>
-  </si>
-  <si>
-    <t>1.1.1.2.05.03</t>
-  </si>
-  <si>
-    <t>1.1.1.2.05.04</t>
-  </si>
-  <si>
-    <t>1.1.1.2.05.05</t>
-  </si>
-  <si>
-    <t>1.1.1.2.06.01</t>
-  </si>
-  <si>
-    <t>1.1.1.2.06.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.06.03</t>
-  </si>
-  <si>
-    <t>1.1.1.2.06.04</t>
-  </si>
-  <si>
-    <t>1.1.1.2.06.05</t>
-  </si>
-  <si>
-    <t>1.1.1.2.07.01</t>
-  </si>
-  <si>
-    <t>Presupuestal - Abono</t>
-  </si>
-  <si>
-    <t>Presupuestal - Cargo</t>
-  </si>
-  <si>
-    <t>Contable - Abono</t>
-  </si>
-  <si>
-    <t>Contable - Cargo</t>
-  </si>
-  <si>
-    <t>8.1.5.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.02</t>
-  </si>
-  <si>
-    <t>1.1.1.2.05.08</t>
-  </si>
-  <si>
-    <t>Por el recaudo de ingresos de Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.5.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.03</t>
-  </si>
-  <si>
-    <t>Por el recaudo de ingresos de Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.5.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>8.1.4.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>1.1.2.2.02.14</t>
   </si>
   <si>
     <t>1.1.1.1.01.01</t>
@@ -578,380 +578,380 @@
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
         <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>32</v>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -976,10 +976,10 @@
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,29 +990,29 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="D31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>32</v>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -1021,12 +1021,12 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
@@ -1035,12 +1035,12 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
@@ -1049,21 +1049,21 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>32</v>
+      <c r="D36" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,7 +1077,7 @@
         <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,7 +1091,7 @@
         <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,12 +1105,12 @@
         <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -1119,7 +1119,7 @@
         <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
